--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484868_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2484868_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>9.839499999999999</v>
+        <v>8.843400000000001</v>
       </c>
       <c r="E2" t="n">
-        <v>7.0662</v>
+        <v>6.5992</v>
       </c>
       <c r="F2" t="n">
-        <v>2.7733</v>
+        <v>2.2442</v>
       </c>
       <c r="G2" t="n">
         <v>2.1166</v>
@@ -610,13 +610,13 @@
         <v>2.6418</v>
       </c>
       <c r="S2" t="n">
-        <v>2.2891</v>
+        <v>1.293</v>
       </c>
       <c r="T2" t="n">
-        <v>1.2461</v>
+        <v>0.7791</v>
       </c>
       <c r="U2" t="n">
-        <v>1.0429</v>
+        <v>0.5139</v>
       </c>
       <c r="V2" t="n">
         <v>3.7356</v>
@@ -631,7 +631,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>J. ESTRELLA MATOS</t>
+          <t>D. SALVADOR ESCUDER</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -643,73 +643,73 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>1.7921</v>
+        <v>3.1172</v>
       </c>
       <c r="E3" t="n">
-        <v>3.3825</v>
+        <v>3.2621</v>
       </c>
       <c r="F3" t="n">
-        <v>-1.5904</v>
+        <v>-0.145</v>
       </c>
       <c r="G3" t="n">
-        <v>1.7244</v>
+        <v>1.2243</v>
       </c>
       <c r="H3" t="n">
-        <v>2.6123</v>
+        <v>2.0128</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.8878</v>
+        <v>-0.7885</v>
       </c>
       <c r="J3" t="n">
-        <v>3.2256</v>
+        <v>2.7799</v>
       </c>
       <c r="K3" t="n">
-        <v>3.7674</v>
+        <v>2.811</v>
       </c>
       <c r="L3" t="n">
-        <v>-0.5417</v>
+        <v>-0.0311</v>
       </c>
       <c r="M3" t="n">
-        <v>-1.5012</v>
+        <v>-1.5556</v>
       </c>
       <c r="N3" t="n">
-        <v>-1.1551</v>
+        <v>-0.7982</v>
       </c>
       <c r="O3" t="n">
-        <v>-0.3461</v>
+        <v>-0.7574</v>
       </c>
       <c r="P3" t="n">
-        <v>1.3209</v>
+        <v>1.5096</v>
       </c>
       <c r="Q3" t="n">
-        <v>-0.9435</v>
+        <v>-1.1322</v>
       </c>
       <c r="R3" t="n">
-        <v>2.2644</v>
+        <v>2.6418</v>
       </c>
       <c r="S3" t="n">
-        <v>-0.9135</v>
+        <v>0.8096</v>
       </c>
       <c r="T3" t="n">
-        <v>-1.3521</v>
+        <v>0.3692</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4386</v>
+        <v>0.4404</v>
       </c>
       <c r="V3" t="n">
-        <v>-0.3398</v>
+        <v>-0.4263</v>
       </c>
       <c r="W3" t="n">
-        <v>2.4524</v>
+        <v>1.2452</v>
       </c>
       <c r="X3" t="n">
-        <v>-2.7922</v>
+        <v>-1.6715</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>D. SALVADOR ESCUDER</t>
+          <t>J. ESTRELLA MATOS</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.725</v>
+        <v>2.9306</v>
       </c>
       <c r="E4" t="n">
-        <v>1.8964</v>
+        <v>4.4945</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.1714</v>
+        <v>-1.5639</v>
       </c>
       <c r="G4" t="n">
-        <v>1.2243</v>
+        <v>1.7244</v>
       </c>
       <c r="H4" t="n">
-        <v>2.0128</v>
+        <v>2.6123</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.7885</v>
+        <v>-0.8878</v>
       </c>
       <c r="J4" t="n">
-        <v>2.7799</v>
+        <v>3.2256</v>
       </c>
       <c r="K4" t="n">
-        <v>2.811</v>
+        <v>3.7674</v>
       </c>
       <c r="L4" t="n">
-        <v>-0.0311</v>
+        <v>-0.5417</v>
       </c>
       <c r="M4" t="n">
-        <v>-1.5556</v>
+        <v>-1.5012</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.7982</v>
+        <v>-1.1551</v>
       </c>
       <c r="O4" t="n">
-        <v>-0.7574</v>
+        <v>-0.3461</v>
       </c>
       <c r="P4" t="n">
-        <v>1.5096</v>
+        <v>1.3209</v>
       </c>
       <c r="Q4" t="n">
-        <v>-1.1322</v>
+        <v>-0.9435</v>
       </c>
       <c r="R4" t="n">
-        <v>2.6418</v>
+        <v>2.2644</v>
       </c>
       <c r="S4" t="n">
-        <v>-0.5826</v>
+        <v>0.225</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.9965000000000001</v>
+        <v>-0.2401</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4139</v>
+        <v>0.465</v>
       </c>
       <c r="V4" t="n">
-        <v>-0.4263</v>
+        <v>-0.3398</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2452</v>
+        <v>2.4524</v>
       </c>
       <c r="X4" t="n">
-        <v>-1.6715</v>
+        <v>-2.7922</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>C. GONZALEZ DIAZ</t>
+          <t>B. MALONE NAVARRO</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.6138</v>
+        <v>0.2896</v>
       </c>
       <c r="E5" t="n">
-        <v>-2.0887</v>
+        <v>-0.3906</v>
       </c>
       <c r="F5" t="n">
-        <v>3.7025</v>
+        <v>0.6802</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.8333</v>
+        <v>-1.1302</v>
       </c>
       <c r="H5" t="n">
-        <v>-3.8418</v>
+        <v>-1.2686</v>
       </c>
       <c r="I5" t="n">
+        <v>0.1384</v>
+      </c>
+      <c r="J5" t="n">
+        <v>-1.2272</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-1.2357</v>
+      </c>
+      <c r="L5" t="n">
         <v>0.008500000000000001</v>
       </c>
-      <c r="J5" t="n">
-        <v>-2.7963</v>
-      </c>
-      <c r="K5" t="n">
-        <v>-2.3283</v>
-      </c>
-      <c r="L5" t="n">
-        <v>-0.468</v>
-      </c>
       <c r="M5" t="n">
-        <v>-1.037</v>
+        <v>0.097</v>
       </c>
       <c r="N5" t="n">
-        <v>-1.5135</v>
+        <v>-0.0329</v>
       </c>
       <c r="O5" t="n">
-        <v>0.4765</v>
+        <v>0.1299</v>
       </c>
       <c r="P5" t="n">
-        <v>1.6983</v>
+        <v>0.3774</v>
       </c>
       <c r="Q5" t="n">
-        <v>-2.0757</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>3.774</v>
+        <v>0.3774</v>
       </c>
       <c r="S5" t="n">
-        <v>3.8733</v>
+        <v>1.0424</v>
       </c>
       <c r="T5" t="n">
-        <v>2.7833</v>
+        <v>0.8366</v>
       </c>
       <c r="U5" t="n">
-        <v>1.09</v>
+        <v>0.2058</v>
       </c>
       <c r="V5" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
         <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.1245</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>B. MALONE NAVARRO</t>
+          <t>C. GONZALEZ DIAZ</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.1136</v>
+        <v>-0.1778</v>
       </c>
       <c r="E6" t="n">
-        <v>0.4863</v>
+        <v>-3.5099</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6273</v>
+        <v>3.3321</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.1302</v>
+        <v>-3.8333</v>
       </c>
       <c r="H6" t="n">
-        <v>-1.2686</v>
+        <v>-3.8418</v>
       </c>
       <c r="I6" t="n">
-        <v>0.1384</v>
+        <v>0.008500000000000001</v>
       </c>
       <c r="J6" t="n">
-        <v>-1.2272</v>
+        <v>-2.7963</v>
       </c>
       <c r="K6" t="n">
-        <v>-1.2357</v>
+        <v>-2.3283</v>
       </c>
       <c r="L6" t="n">
-        <v>0.008500000000000001</v>
+        <v>-0.468</v>
       </c>
       <c r="M6" t="n">
-        <v>0.097</v>
+        <v>-1.037</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.0329</v>
+        <v>-1.5135</v>
       </c>
       <c r="O6" t="n">
-        <v>0.1299</v>
+        <v>0.4765</v>
       </c>
       <c r="P6" t="n">
-        <v>0.3774</v>
+        <v>1.6983</v>
       </c>
       <c r="Q6" t="n">
-        <v>0</v>
+        <v>-2.0757</v>
       </c>
       <c r="R6" t="n">
-        <v>0.3774</v>
+        <v>3.774</v>
       </c>
       <c r="S6" t="n">
-        <v>1.8664</v>
+        <v>2.0817</v>
       </c>
       <c r="T6" t="n">
-        <v>1.7135</v>
+        <v>1.3621</v>
       </c>
       <c r="U6" t="n">
-        <v>0.1528</v>
+        <v>0.7196</v>
       </c>
       <c r="V6" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
       <c r="W6" t="n">
         <v>0</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.1245</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-1.3325</v>
+        <v>-0.7252999999999999</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.5658</v>
+        <v>-0.1173</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.7667</v>
+        <v>-0.608</v>
       </c>
       <c r="G7" t="n">
         <v>-4.0908</v>
@@ -1000,13 +1000,13 @@
         <v>2.2644</v>
       </c>
       <c r="S7" t="n">
-        <v>0.3809</v>
+        <v>0.9881</v>
       </c>
       <c r="T7" t="n">
-        <v>0.1234</v>
+        <v>0.5719</v>
       </c>
       <c r="U7" t="n">
-        <v>0.2575</v>
+        <v>0.4162</v>
       </c>
       <c r="V7" t="n">
         <v>1.2452</v>
@@ -1021,7 +1021,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>W. LADSON BUGALLO</t>
+          <t>M. MARISCAL GOMEZ</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -1033,67 +1033,67 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.7696</v>
+        <v>-2.5673</v>
       </c>
       <c r="E8" t="n">
-        <v>-1.5187</v>
+        <v>-2.6413</v>
       </c>
       <c r="F8" t="n">
-        <v>-1.2509</v>
+        <v>0.074</v>
       </c>
       <c r="G8" t="n">
-        <v>-2.509</v>
+        <v>-4.4049</v>
       </c>
       <c r="H8" t="n">
-        <v>-0.7489</v>
+        <v>-2.383</v>
       </c>
       <c r="I8" t="n">
-        <v>-1.7601</v>
+        <v>-2.0219</v>
       </c>
       <c r="J8" t="n">
-        <v>-0.7211</v>
+        <v>-1.8257</v>
       </c>
       <c r="K8" t="n">
-        <v>0.4547</v>
+        <v>-0.6911</v>
       </c>
       <c r="L8" t="n">
-        <v>-1.1757</v>
+        <v>-1.1346</v>
       </c>
       <c r="M8" t="n">
-        <v>-1.788</v>
+        <v>-2.5792</v>
       </c>
       <c r="N8" t="n">
-        <v>-1.2036</v>
+        <v>-1.6919</v>
       </c>
       <c r="O8" t="n">
-        <v>-0.5843</v>
+        <v>-0.8873</v>
       </c>
       <c r="P8" t="n">
-        <v>-0.5661</v>
+        <v>2.4531</v>
       </c>
       <c r="Q8" t="n">
-        <v>-2.0757</v>
+        <v>-0.9435</v>
       </c>
       <c r="R8" t="n">
-        <v>1.5096</v>
+        <v>3.3966</v>
       </c>
       <c r="S8" t="n">
-        <v>2.2978</v>
+        <v>0.1127</v>
       </c>
       <c r="T8" t="n">
-        <v>1.5989</v>
+        <v>0.1279</v>
       </c>
       <c r="U8" t="n">
-        <v>0.699</v>
+        <v>-0.0152</v>
       </c>
       <c r="V8" t="n">
-        <v>-1.9923</v>
+        <v>-0.7281</v>
       </c>
       <c r="W8" t="n">
-        <v>-0.3208</v>
+        <v>0</v>
       </c>
       <c r="X8" t="n">
-        <v>-1.6715</v>
+        <v>-0.7281</v>
       </c>
     </row>
     <row r="9">
@@ -1111,13 +1111,13 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-3.2511</v>
+        <v>-2.6476</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.9301</v>
+        <v>-1.6177</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.3209</v>
+        <v>-1.0299</v>
       </c>
       <c r="G9" t="n">
         <v>-2.4658</v>
@@ -1156,13 +1156,13 @@
         <v>1.887</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1504</v>
+        <v>0.7539</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.1706</v>
+        <v>0.1419</v>
       </c>
       <c r="U9" t="n">
-        <v>0.321</v>
+        <v>0.612</v>
       </c>
       <c r="V9" t="n">
         <v>-1.6905</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. MARISCAL GOMEZ</t>
+          <t>W. LADSON BUGALLO</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,67 +1189,67 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-4.8821</v>
+        <v>-3.7444</v>
       </c>
       <c r="E10" t="n">
-        <v>-4.5328</v>
+        <v>-2.4141</v>
       </c>
       <c r="F10" t="n">
-        <v>-0.3493</v>
+        <v>-1.3303</v>
       </c>
       <c r="G10" t="n">
-        <v>-4.4049</v>
+        <v>-2.509</v>
       </c>
       <c r="H10" t="n">
-        <v>-2.383</v>
+        <v>-0.7489</v>
       </c>
       <c r="I10" t="n">
-        <v>-2.0219</v>
+        <v>-1.7601</v>
       </c>
       <c r="J10" t="n">
-        <v>-1.8257</v>
+        <v>-0.7211</v>
       </c>
       <c r="K10" t="n">
-        <v>-0.6911</v>
+        <v>0.4547</v>
       </c>
       <c r="L10" t="n">
-        <v>-1.1346</v>
+        <v>-1.1757</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.5792</v>
+        <v>-1.788</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.6919</v>
+        <v>-1.2036</v>
       </c>
       <c r="O10" t="n">
-        <v>-0.8873</v>
+        <v>-0.5843</v>
       </c>
       <c r="P10" t="n">
-        <v>2.4531</v>
+        <v>-0.5661</v>
       </c>
       <c r="Q10" t="n">
-        <v>-0.9435</v>
+        <v>-2.0757</v>
       </c>
       <c r="R10" t="n">
-        <v>3.3966</v>
+        <v>1.5096</v>
       </c>
       <c r="S10" t="n">
-        <v>-2.2021</v>
+        <v>1.3231</v>
       </c>
       <c r="T10" t="n">
-        <v>-1.7636</v>
+        <v>0.7034</v>
       </c>
       <c r="U10" t="n">
-        <v>-0.4385</v>
+        <v>0.6196</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.7281</v>
+        <v>-1.9923</v>
       </c>
       <c r="W10" t="n">
-        <v>0</v>
+        <v>-0.3208</v>
       </c>
       <c r="X10" t="n">
-        <v>-0.7281</v>
+        <v>-1.6715</v>
       </c>
     </row>
     <row r="11">
@@ -1267,31 +1267,31 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>3.848699999999998</v>
+        <v>5.3184</v>
       </c>
       <c r="E11" t="n">
-        <v>2.195300000000001</v>
+        <v>3.664899999999999</v>
       </c>
       <c r="F11" t="n">
-        <v>1.653500000000001</v>
+        <v>1.6534</v>
       </c>
       <c r="G11" t="n">
         <v>-13.3687</v>
       </c>
       <c r="H11" t="n">
-        <v>-5.681800000000001</v>
+        <v>-5.6818</v>
       </c>
       <c r="I11" t="n">
         <v>-7.686999999999999</v>
       </c>
       <c r="J11" t="n">
-        <v>0.1281999999999999</v>
+        <v>0.1281999999999995</v>
       </c>
       <c r="K11" t="n">
-        <v>4.5701</v>
+        <v>4.570099999999999</v>
       </c>
       <c r="L11" t="n">
-        <v>-4.4416</v>
+        <v>-4.441599999999999</v>
       </c>
       <c r="M11" t="n">
         <v>-13.497</v>
@@ -1312,28 +1312,28 @@
         <v>20.757</v>
       </c>
       <c r="S11" t="n">
-        <v>7.159699999999999</v>
+        <v>8.6295</v>
       </c>
       <c r="T11" t="n">
-        <v>3.182399999999999</v>
+        <v>4.652</v>
       </c>
       <c r="U11" t="n">
-        <v>3.9772</v>
+        <v>3.977300000000001</v>
       </c>
       <c r="V11" t="n">
-        <v>-0.3207</v>
+        <v>-0.3206999999999995</v>
       </c>
       <c r="W11" t="n">
         <v>9.263</v>
       </c>
       <c r="X11" t="n">
-        <v>-9.583699999999999</v>
+        <v>-9.5837</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>A. VILAGRAN GONZALEZ</t>
+          <t>I. BARBERO LOPEZ</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,73 +1345,73 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>3.6499</v>
+        <v>2.7875</v>
       </c>
       <c r="E12" t="n">
-        <v>2.4053</v>
+        <v>0.6259</v>
       </c>
       <c r="F12" t="n">
-        <v>1.2446</v>
+        <v>2.1616</v>
       </c>
       <c r="G12" t="n">
-        <v>0.4375</v>
+        <v>2.6549</v>
       </c>
       <c r="H12" t="n">
-        <v>0.4571</v>
+        <v>2.5505</v>
       </c>
       <c r="I12" t="n">
-        <v>-0.0196</v>
+        <v>0.1044</v>
       </c>
       <c r="J12" t="n">
-        <v>0.3155</v>
+        <v>2.3275</v>
       </c>
       <c r="K12" t="n">
-        <v>0.8984</v>
+        <v>2.8948</v>
       </c>
       <c r="L12" t="n">
-        <v>-0.5829</v>
+        <v>-0.5673</v>
       </c>
       <c r="M12" t="n">
-        <v>0.122</v>
+        <v>0.3274</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4413</v>
+        <v>-0.3443</v>
       </c>
       <c r="O12" t="n">
-        <v>0.5633</v>
+        <v>0.6717</v>
       </c>
       <c r="P12" t="n">
-        <v>1.3209</v>
+        <v>-0.7548</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1887</v>
+        <v>-2.2644</v>
       </c>
       <c r="R12" t="n">
         <v>1.5096</v>
       </c>
       <c r="S12" t="n">
-        <v>0.3445</v>
+        <v>-0.3578</v>
       </c>
       <c r="T12" t="n">
-        <v>0.4296</v>
+        <v>-0.6824</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0851</v>
+        <v>0.3246</v>
       </c>
       <c r="V12" t="n">
-        <v>1.547</v>
+        <v>1.2452</v>
       </c>
       <c r="W12" t="n">
-        <v>1.8488</v>
+        <v>1.2452</v>
       </c>
       <c r="X12" t="n">
-        <v>-0.3018</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>P. NAKIDJIM</t>
+          <t>A. VILAGRAN GONZALEZ</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -1423,73 +1423,73 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>3.1578</v>
+        <v>2.7743</v>
       </c>
       <c r="E13" t="n">
-        <v>1.1128</v>
+        <v>1.8207</v>
       </c>
       <c r="F13" t="n">
-        <v>2.0451</v>
+        <v>0.9536</v>
       </c>
       <c r="G13" t="n">
-        <v>7.0907</v>
+        <v>0.4375</v>
       </c>
       <c r="H13" t="n">
-        <v>5.9039</v>
+        <v>0.4571</v>
       </c>
       <c r="I13" t="n">
-        <v>1.1868</v>
+        <v>-0.0196</v>
       </c>
       <c r="J13" t="n">
-        <v>5.371</v>
+        <v>0.3155</v>
       </c>
       <c r="K13" t="n">
-        <v>5.2887</v>
+        <v>0.8984</v>
       </c>
       <c r="L13" t="n">
-        <v>0.0823</v>
+        <v>-0.5829</v>
       </c>
       <c r="M13" t="n">
-        <v>1.7197</v>
+        <v>0.122</v>
       </c>
       <c r="N13" t="n">
-        <v>0.6152</v>
+        <v>-0.4413</v>
       </c>
       <c r="O13" t="n">
-        <v>1.1045</v>
+        <v>0.5633</v>
       </c>
       <c r="P13" t="n">
-        <v>-3.5853</v>
+        <v>1.3209</v>
       </c>
       <c r="Q13" t="n">
-        <v>-5.0949</v>
+        <v>-0.1887</v>
       </c>
       <c r="R13" t="n">
         <v>1.5096</v>
       </c>
       <c r="S13" t="n">
-        <v>1.5203</v>
+        <v>-0.5311</v>
       </c>
       <c r="T13" t="n">
-        <v>0.5349</v>
+        <v>-0.155</v>
       </c>
       <c r="U13" t="n">
-        <v>0.9854000000000001</v>
+        <v>-0.3761</v>
       </c>
       <c r="V13" t="n">
-        <v>-1.8678</v>
+        <v>1.547</v>
       </c>
       <c r="W13" t="n">
-        <v>0.3018</v>
+        <v>1.8488</v>
       </c>
       <c r="X13" t="n">
-        <v>-2.1696</v>
+        <v>-0.3018</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>I. BARBERO LOPEZ</t>
+          <t>P. NAKIDJIM</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1501,67 +1501,67 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>2.9114</v>
+        <v>1.6557</v>
       </c>
       <c r="E14" t="n">
-        <v>0.7233000000000001</v>
+        <v>0.4307</v>
       </c>
       <c r="F14" t="n">
-        <v>2.188</v>
+        <v>1.225</v>
       </c>
       <c r="G14" t="n">
-        <v>2.6549</v>
+        <v>7.0907</v>
       </c>
       <c r="H14" t="n">
-        <v>2.5505</v>
+        <v>5.9039</v>
       </c>
       <c r="I14" t="n">
-        <v>0.1044</v>
+        <v>1.1868</v>
       </c>
       <c r="J14" t="n">
-        <v>2.3275</v>
+        <v>5.371</v>
       </c>
       <c r="K14" t="n">
-        <v>2.8948</v>
+        <v>5.2887</v>
       </c>
       <c r="L14" t="n">
-        <v>-0.5673</v>
+        <v>0.0823</v>
       </c>
       <c r="M14" t="n">
-        <v>0.3274</v>
+        <v>1.7197</v>
       </c>
       <c r="N14" t="n">
-        <v>-0.3443</v>
+        <v>0.6152</v>
       </c>
       <c r="O14" t="n">
-        <v>0.6717</v>
+        <v>1.1045</v>
       </c>
       <c r="P14" t="n">
-        <v>-0.7548</v>
+        <v>-3.5853</v>
       </c>
       <c r="Q14" t="n">
-        <v>-2.2644</v>
+        <v>-5.0949</v>
       </c>
       <c r="R14" t="n">
         <v>1.5096</v>
       </c>
       <c r="S14" t="n">
-        <v>-0.2339</v>
+        <v>0.0182</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.585</v>
+        <v>-0.1472</v>
       </c>
       <c r="U14" t="n">
-        <v>0.3511</v>
+        <v>0.1653</v>
       </c>
       <c r="V14" t="n">
-        <v>1.2452</v>
+        <v>-1.8678</v>
       </c>
       <c r="W14" t="n">
-        <v>1.2452</v>
+        <v>0.3018</v>
       </c>
       <c r="X14" t="n">
-        <v>0</v>
+        <v>-2.1696</v>
       </c>
     </row>
     <row r="15">
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>-0.659</v>
+        <v>-0.4989</v>
       </c>
       <c r="E17" t="n">
-        <v>1.585</v>
+        <v>1.8773</v>
       </c>
       <c r="F17" t="n">
-        <v>-2.244</v>
+        <v>-2.3762</v>
       </c>
       <c r="G17" t="n">
         <v>1.3337</v>
@@ -1780,13 +1780,13 @@
         <v>0.7548</v>
       </c>
       <c r="S17" t="n">
-        <v>-1.2944</v>
+        <v>-1.1344</v>
       </c>
       <c r="T17" t="n">
-        <v>-0.9994</v>
+        <v>-0.7071</v>
       </c>
       <c r="U17" t="n">
-        <v>-0.295</v>
+        <v>-0.4273</v>
       </c>
       <c r="V17" t="n">
         <v>0.6226</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5581</v>
+        <v>-0.8774</v>
       </c>
       <c r="E18" t="n">
-        <v>-0.5597</v>
+        <v>-0.17</v>
       </c>
       <c r="F18" t="n">
-        <v>-0.9984</v>
+        <v>-0.7074</v>
       </c>
       <c r="G18" t="n">
         <v>-1.1524</v>
@@ -1858,13 +1858,13 @@
         <v>1.1322</v>
       </c>
       <c r="S18" t="n">
-        <v>-1.0093</v>
+        <v>-0.3286</v>
       </c>
       <c r="T18" t="n">
-        <v>-0.6343</v>
+        <v>-0.2446</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.375</v>
+        <v>-0.08400000000000001</v>
       </c>
       <c r="V18" t="n">
         <v>0.6036</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.6671</v>
+        <v>-1.2076</v>
       </c>
       <c r="E19" t="n">
-        <v>-2.5503</v>
+        <v>-2.3555</v>
       </c>
       <c r="F19" t="n">
-        <v>0.8833</v>
+        <v>1.1478</v>
       </c>
       <c r="G19" t="n">
         <v>0.5487</v>
@@ -1936,13 +1936,13 @@
         <v>0.3774</v>
       </c>
       <c r="S19" t="n">
-        <v>-1.027</v>
+        <v>-0.5675</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.2228</v>
+        <v>-0.0279</v>
       </c>
       <c r="U19" t="n">
-        <v>-0.8041</v>
+        <v>-0.5396</v>
       </c>
       <c r="V19" t="n">
         <v>0.3208</v>
@@ -1969,13 +1969,13 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-2.0864</v>
+        <v>-1.7592</v>
       </c>
       <c r="E20" t="n">
-        <v>-1.1426</v>
+        <v>-0.9477</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.9438</v>
+        <v>-0.8115</v>
       </c>
       <c r="G20" t="n">
         <v>3.5268</v>
@@ -2014,13 +2014,13 @@
         <v>1.5096</v>
       </c>
       <c r="S20" t="n">
-        <v>-1.613</v>
+        <v>-1.2859</v>
       </c>
       <c r="T20" t="n">
-        <v>-0.5879</v>
+        <v>-0.393</v>
       </c>
       <c r="U20" t="n">
-        <v>-1.0251</v>
+        <v>-0.8929</v>
       </c>
       <c r="V20" t="n">
         <v>-1.547</v>
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-4.9526</v>
+        <v>-4.1312</v>
       </c>
       <c r="E21" t="n">
-        <v>-2.4991</v>
+        <v>-2.2068</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.4536</v>
+        <v>-1.9245</v>
       </c>
       <c r="G21" t="n">
         <v>-1.7889</v>
@@ -2092,13 +2092,13 @@
         <v>1.1322</v>
       </c>
       <c r="S21" t="n">
-        <v>-2.8428</v>
+        <v>-2.0214</v>
       </c>
       <c r="T21" t="n">
-        <v>-1.3986</v>
+        <v>-1.1063</v>
       </c>
       <c r="U21" t="n">
-        <v>-1.4443</v>
+        <v>-0.9152</v>
       </c>
       <c r="V21" t="n">
         <v>0.6226</v>
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-5.4464</v>
+        <v>-5.3935</v>
       </c>
       <c r="E22" t="n">
         <v>-3.5299</v>
       </c>
       <c r="F22" t="n">
-        <v>-1.9166</v>
+        <v>-1.8637</v>
       </c>
       <c r="G22" t="n">
         <v>-2.084</v>
@@ -2170,13 +2170,13 @@
         <v>0.9435</v>
       </c>
       <c r="S22" t="n">
-        <v>-1.004</v>
+        <v>-0.9510999999999999</v>
       </c>
       <c r="T22" t="n">
         <v>-0.5139</v>
       </c>
       <c r="U22" t="n">
-        <v>-0.4902</v>
+        <v>-0.4373</v>
       </c>
       <c r="V22" t="n">
         <v>-1.2262</v>
@@ -2203,19 +2203,19 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.848799999999998</v>
+        <v>-3.8486</v>
       </c>
       <c r="E23" t="n">
-        <v>-1.653499999999999</v>
+        <v>-1.6536</v>
       </c>
       <c r="F23" t="n">
-        <v>-2.195399999999999</v>
+        <v>-2.1953</v>
       </c>
       <c r="G23" t="n">
         <v>13.3687</v>
       </c>
       <c r="H23" t="n">
-        <v>5.6818</v>
+        <v>5.681800000000002</v>
       </c>
       <c r="I23" t="n">
         <v>7.687</v>
@@ -2230,7 +2230,7 @@
         <v>3.245299999999999</v>
       </c>
       <c r="M23" t="n">
-        <v>-0.1284</v>
+        <v>-0.1283999999999996</v>
       </c>
       <c r="N23" t="n">
         <v>-4.5699</v>
@@ -2248,16 +2248,16 @@
         <v>10.3785</v>
       </c>
       <c r="S23" t="n">
-        <v>-7.159599999999999</v>
+        <v>-7.1596</v>
       </c>
       <c r="T23" t="n">
         <v>-3.9774</v>
       </c>
       <c r="U23" t="n">
-        <v>-3.1823</v>
+        <v>-3.1825</v>
       </c>
       <c r="V23" t="n">
-        <v>0.3208000000000002</v>
+        <v>0.3208000000000006</v>
       </c>
       <c r="W23" t="n">
         <v>9.5838</v>
